--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486952_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486952_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.276300000000001</v>
+        <v>8.8612</v>
       </c>
       <c r="E2" t="n">
-        <v>6.2528</v>
+        <v>7.4306</v>
       </c>
       <c r="F2" t="n">
-        <v>2.0235</v>
+        <v>1.4306</v>
       </c>
       <c r="G2" t="n">
         <v>5.7972</v>
@@ -610,13 +610,13 @@
         <v>2.6694</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7091</v>
+        <v>1.2941</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.8409</v>
+        <v>0.3369</v>
       </c>
       <c r="U2" t="n">
-        <v>1.55</v>
+        <v>0.9572000000000001</v>
       </c>
       <c r="V2" t="n">
         <v>4.2341</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.759</v>
+        <v>3.3373</v>
       </c>
       <c r="E3" t="n">
-        <v>4.1787</v>
+        <v>4.0237</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.4196</v>
+        <v>-0.6864</v>
       </c>
       <c r="G3" t="n">
         <v>1.6631</v>
@@ -688,13 +688,13 @@
         <v>2.0534</v>
       </c>
       <c r="S3" t="n">
-        <v>1.1123</v>
+        <v>0.6906</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.0468</v>
+        <v>-0.2017</v>
       </c>
       <c r="U3" t="n">
-        <v>1.1591</v>
+        <v>0.8923</v>
       </c>
       <c r="V3" t="n">
         <v>-1.0698</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>O. BRAMBLE</t>
+          <t>J. HIERREZUELO SERER</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.8863</v>
+        <v>1.6462</v>
       </c>
       <c r="E4" t="n">
-        <v>2.4539</v>
+        <v>0.4493</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4324</v>
+        <v>1.1969</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.7055</v>
+        <v>0.4713</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2336</v>
+        <v>1.2974</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.9391</v>
+        <v>-0.8260999999999999</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.8825</v>
+        <v>0.5656</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.3825</v>
+        <v>0.4866</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.5</v>
+        <v>0.0789</v>
       </c>
       <c r="M4" t="n">
-        <v>0.177</v>
+        <v>-0.09429999999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>0.6161</v>
+        <v>0.8107</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.4391</v>
+        <v>-0.905</v>
       </c>
       <c r="P4" t="n">
+        <v>1.0267</v>
+      </c>
+      <c r="Q4" t="n">
         <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>-1.0267</v>
       </c>
       <c r="R4" t="n">
         <v>1.0267</v>
       </c>
       <c r="S4" t="n">
-        <v>3.3516</v>
+        <v>0.1482</v>
       </c>
       <c r="T4" t="n">
-        <v>2.704</v>
+        <v>-0.1163</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6476</v>
+        <v>0.2645</v>
       </c>
       <c r="V4" t="n">
-        <v>0.2402</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.6591</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.4189</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. HIERREZUELO SERER</t>
+          <t>O. BRAMBLE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.7385</v>
+        <v>1.5058</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8677</v>
+        <v>1.0437</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8708</v>
+        <v>0.462</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4713</v>
+        <v>-0.7055</v>
       </c>
       <c r="H5" t="n">
-        <v>1.2974</v>
+        <v>0.2336</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.8260999999999999</v>
+        <v>-0.9391</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5656</v>
+        <v>-0.8825</v>
       </c>
       <c r="K5" t="n">
-        <v>0.4866</v>
+        <v>-0.3825</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0789</v>
+        <v>-0.5</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.09429999999999999</v>
+        <v>0.177</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8107</v>
+        <v>0.6161</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.905</v>
+        <v>-0.4391</v>
       </c>
       <c r="P5" t="n">
-        <v>1.0267</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.0267</v>
       </c>
       <c r="R5" t="n">
         <v>1.0267</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2406</v>
+        <v>1.9711</v>
       </c>
       <c r="T5" t="n">
-        <v>0.3021</v>
+        <v>1.2939</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0616</v>
+        <v>0.6772</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.2402</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.6591</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-1.4189</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>B. VANACLOCHA SANCHEZ</t>
+          <t>F. ANDRADE AMIEL</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1757</v>
+        <v>0.5357</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7529</v>
+        <v>-1.8678</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.5770999999999999</v>
+        <v>2.4034</v>
       </c>
       <c r="G6" t="n">
-        <v>-3.1576</v>
+        <v>-0.2596</v>
       </c>
       <c r="H6" t="n">
-        <v>-2.066</v>
+        <v>3.0138</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.0916</v>
+        <v>-3.2733</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.6532</v>
+        <v>-0.5813</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.9295</v>
+        <v>2.0897</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2763</v>
+        <v>-2.671</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.5044</v>
+        <v>0.3218</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.1365</v>
+        <v>0.9241</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.3679</v>
+        <v>-0.6022999999999999</v>
       </c>
       <c r="P6" t="n">
-        <v>0.616</v>
+        <v>0.4107</v>
       </c>
       <c r="Q6" t="n">
         <v>-1.0267</v>
       </c>
       <c r="R6" t="n">
-        <v>1.6427</v>
+        <v>1.4374</v>
       </c>
       <c r="S6" t="n">
-        <v>3.3066</v>
+        <v>0.3846</v>
       </c>
       <c r="T6" t="n">
-        <v>2.8435</v>
+        <v>-0.2597</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4631</v>
+        <v>0.6443</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.5893</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0.5893</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.1786</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>F. ANDRADE AMIEL</t>
+          <t>J. GONZALEZ ALBADALEJO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2739</v>
+        <v>-0.5415</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.5884</v>
+        <v>-1.4839</v>
       </c>
       <c r="F7" t="n">
-        <v>2.3145</v>
+        <v>0.9425</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.2596</v>
+        <v>0.7495000000000001</v>
       </c>
       <c r="H7" t="n">
-        <v>3.0138</v>
+        <v>0.7524999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>-3.2733</v>
+        <v>-0.003</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.5813</v>
+        <v>0.6277</v>
       </c>
       <c r="K7" t="n">
-        <v>2.0897</v>
+        <v>-0.2268</v>
       </c>
       <c r="L7" t="n">
-        <v>-2.671</v>
+        <v>0.8545</v>
       </c>
       <c r="M7" t="n">
-        <v>0.3218</v>
+        <v>0.1218</v>
       </c>
       <c r="N7" t="n">
-        <v>0.9241</v>
+        <v>0.9792999999999999</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.6022999999999999</v>
+        <v>-0.8575</v>
       </c>
       <c r="P7" t="n">
-        <v>0.4107</v>
+        <v>-0.4107</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.0267</v>
+        <v>-2.0534</v>
       </c>
       <c r="R7" t="n">
-        <v>1.4374</v>
+        <v>1.6427</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.425</v>
+        <v>0.2984</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.9804</v>
+        <v>-0.0582</v>
       </c>
       <c r="U7" t="n">
-        <v>0.5554</v>
+        <v>0.3566</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-1.1786</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. GONZALEZ ALBADALEJO</t>
+          <t>B. VANACLOCHA SANCHEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.827</v>
+        <v>-1.4098</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.4138</v>
+        <v>-0.6844</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5868</v>
+        <v>-0.7252999999999999</v>
       </c>
       <c r="G8" t="n">
-        <v>0.7495000000000001</v>
+        <v>-3.1576</v>
       </c>
       <c r="H8" t="n">
-        <v>0.7524999999999999</v>
+        <v>-2.066</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.003</v>
+        <v>-1.0916</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6277</v>
+        <v>-1.6532</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.2268</v>
+        <v>-1.9295</v>
       </c>
       <c r="L8" t="n">
-        <v>0.8545</v>
+        <v>0.2763</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1218</v>
+        <v>-1.5044</v>
       </c>
       <c r="N8" t="n">
-        <v>0.9792999999999999</v>
+        <v>-0.1365</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.8575</v>
+        <v>-1.3679</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.4107</v>
+        <v>0.616</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.0534</v>
+        <v>-1.0267</v>
       </c>
       <c r="R8" t="n">
         <v>1.6427</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.9872</v>
+        <v>1.7211</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.9881</v>
+        <v>1.4062</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0009</v>
+        <v>0.3149</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.1786</v>
+        <v>-0.5893</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.5893</v>
       </c>
       <c r="X8" t="n">
         <v>-1.1786</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.7657</v>
+        <v>-2.0329</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.6087</v>
+        <v>-1.0242</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.1569</v>
+        <v>-1.0087</v>
       </c>
       <c r="G9" t="n">
         <v>-2.0152</v>
@@ -1156,13 +1156,13 @@
         <v>1.8481</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.8038999999999999</v>
+        <v>0.9288999999999999</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.3679</v>
+        <v>0.2167</v>
       </c>
       <c r="U9" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.7122000000000001</v>
       </c>
       <c r="V9" t="n">
         <v>-1.7679</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.1176</v>
+        <v>-4.4036</v>
       </c>
       <c r="E10" t="n">
-        <v>-5.1148</v>
+        <v>-4.46</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.0028</v>
+        <v>0.0565</v>
       </c>
       <c r="G10" t="n">
         <v>-2.1901</v>
@@ -1234,13 +1234,13 @@
         <v>1.0267</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3053</v>
+        <v>0.4088</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7169</v>
+        <v>-0.0621</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4116</v>
+        <v>0.4709</v>
       </c>
       <c r="V10" t="n">
         <v>0.4579</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>5.8516</v>
+        <v>7.498400000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>1.7803</v>
+        <v>3.427</v>
       </c>
       <c r="F11" t="n">
-        <v>4.0716</v>
+        <v>4.0715</v>
       </c>
       <c r="G11" t="n">
         <v>0.3530999999999995</v>
@@ -1312,16 +1312,16 @@
         <v>14.3738</v>
       </c>
       <c r="S11" t="n">
-        <v>6.198800000000001</v>
+        <v>7.845800000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>0.9086000000000006</v>
+        <v>2.5557</v>
       </c>
       <c r="U11" t="n">
-        <v>5.2901</v>
+        <v>5.290100000000001</v>
       </c>
       <c r="V11" t="n">
-        <v>0.3265999999999996</v>
+        <v>0.3266</v>
       </c>
       <c r="W11" t="n">
         <v>8.032599999999999</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>6.8512</v>
+        <v>6.7448</v>
       </c>
       <c r="E12" t="n">
         <v>4.7956</v>
       </c>
       <c r="F12" t="n">
-        <v>2.0555</v>
+        <v>1.9491</v>
       </c>
       <c r="G12" t="n">
         <v>4.1854</v>
@@ -1390,13 +1390,13 @@
         <v>2.6694</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0416</v>
+        <v>-0.0649</v>
       </c>
       <c r="T12" t="n">
         <v>-0.8758</v>
       </c>
       <c r="U12" t="n">
-        <v>0.9174</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="V12" t="n">
         <v>2.0082</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>J. CASTILLO CARRASCO</t>
+          <t>J. BOIX COLET</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.0143</v>
+        <v>1.6742</v>
       </c>
       <c r="E13" t="n">
-        <v>1.59</v>
+        <v>-0.3489</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.5756</v>
+        <v>2.023</v>
       </c>
       <c r="G13" t="n">
-        <v>2.9687</v>
+        <v>1.2955</v>
       </c>
       <c r="H13" t="n">
-        <v>0.4084</v>
+        <v>1.3036</v>
       </c>
       <c r="I13" t="n">
-        <v>2.5603</v>
+        <v>-0.008</v>
       </c>
       <c r="J13" t="n">
-        <v>2.7021</v>
+        <v>1.239</v>
       </c>
       <c r="K13" t="n">
-        <v>0.0973</v>
+        <v>0.7397</v>
       </c>
       <c r="L13" t="n">
-        <v>2.6047</v>
+        <v>0.4993</v>
       </c>
       <c r="M13" t="n">
-        <v>0.2666</v>
+        <v>0.0566</v>
       </c>
       <c r="N13" t="n">
-        <v>0.311</v>
+        <v>0.5639</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.0445</v>
+        <v>-0.5073</v>
       </c>
       <c r="P13" t="n">
-        <v>0.8214</v>
+        <v>0.616</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.0267</v>
+        <v>-2.0534</v>
       </c>
       <c r="R13" t="n">
-        <v>1.8481</v>
+        <v>2.6694</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.4184</v>
+        <v>-1.6563</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.0854</v>
+        <v>-1.1935</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.333</v>
+        <v>-0.4627</v>
       </c>
       <c r="V13" t="n">
-        <v>-2.3573</v>
+        <v>1.4189</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.6591</v>
       </c>
       <c r="X13" t="n">
-        <v>-2.3573</v>
+        <v>-0.2402</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J. BOIX COLET</t>
+          <t>J. CASTILLO CARRASCO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.785</v>
+        <v>1.1538</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.6627</v>
+        <v>1.59</v>
       </c>
       <c r="F14" t="n">
-        <v>1.4477</v>
+        <v>-0.4362</v>
       </c>
       <c r="G14" t="n">
-        <v>1.2955</v>
+        <v>2.9687</v>
       </c>
       <c r="H14" t="n">
-        <v>1.3036</v>
+        <v>0.4084</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.008</v>
+        <v>2.5603</v>
       </c>
       <c r="J14" t="n">
-        <v>1.239</v>
+        <v>2.7021</v>
       </c>
       <c r="K14" t="n">
-        <v>0.7397</v>
+        <v>0.0973</v>
       </c>
       <c r="L14" t="n">
-        <v>0.4993</v>
+        <v>2.6047</v>
       </c>
       <c r="M14" t="n">
-        <v>0.0566</v>
+        <v>0.2666</v>
       </c>
       <c r="N14" t="n">
-        <v>0.5639</v>
+        <v>0.311</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.5073</v>
+        <v>-0.0445</v>
       </c>
       <c r="P14" t="n">
-        <v>0.616</v>
+        <v>0.8214</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.0534</v>
+        <v>-1.0267</v>
       </c>
       <c r="R14" t="n">
-        <v>2.6694</v>
+        <v>1.8481</v>
       </c>
       <c r="S14" t="n">
-        <v>-2.5454</v>
+        <v>-0.2789</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.5073</v>
+        <v>-0.0854</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.0381</v>
+        <v>-0.1936</v>
       </c>
       <c r="V14" t="n">
-        <v>1.4189</v>
+        <v>-2.3573</v>
       </c>
       <c r="W14" t="n">
-        <v>1.6591</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.2402</v>
+        <v>-2.3573</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6595</v>
+        <v>0.7118</v>
       </c>
       <c r="E15" t="n">
-        <v>1.5531</v>
+        <v>1.03</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.8935999999999999</v>
+        <v>-0.3182</v>
       </c>
       <c r="G15" t="n">
         <v>0.6827</v>
@@ -1624,13 +1624,13 @@
         <v>2.8748</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.0849</v>
+        <v>-1.0325</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.0468</v>
+        <v>-0.5698</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.0381</v>
+        <v>-0.4627</v>
       </c>
       <c r="V15" t="n">
         <v>0.2402</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.0472</v>
+        <v>-0.06569999999999999</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.069</v>
+        <v>-0.3368</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0218</v>
+        <v>0.2711</v>
       </c>
       <c r="G16" t="n">
         <v>2.1309</v>
@@ -1702,13 +1702,13 @@
         <v>2.0534</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.6934</v>
+        <v>-0.7119</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.4415</v>
+        <v>-0.7092000000000001</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2519</v>
+        <v>-0.0027</v>
       </c>
       <c r="V16" t="n">
         <v>-0.4579</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. TOMAIC TOMAIC</t>
+          <t>F. GARRIDO TEBAN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-2.029</v>
+        <v>-1.788</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.6359</v>
+        <v>-1.0561</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.3932</v>
+        <v>-0.7319</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.1166</v>
+        <v>-1.1183</v>
       </c>
       <c r="H17" t="n">
-        <v>-4.2136</v>
+        <v>-0.8501</v>
       </c>
       <c r="I17" t="n">
-        <v>2.097</v>
+        <v>-0.2682</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.4045</v>
+        <v>-0.5795</v>
       </c>
       <c r="K17" t="n">
-        <v>-2.8249</v>
+        <v>-0.6584</v>
       </c>
       <c r="L17" t="n">
-        <v>2.4204</v>
+        <v>0.0789</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.7121</v>
+        <v>-0.5387999999999999</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.3887</v>
+        <v>-0.1917</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.3234</v>
+        <v>-0.3472</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.8214</v>
+        <v>0.2053</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.0534</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.2321</v>
+        <v>0.2053</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3196</v>
+        <v>-0.2858</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3566</v>
+        <v>-0.4767</v>
       </c>
       <c r="U17" t="n">
-        <v>0.6762</v>
+        <v>0.1909</v>
       </c>
       <c r="V17" t="n">
-        <v>0.5893</v>
+        <v>-0.5893</v>
       </c>
       <c r="W17" t="n">
-        <v>1.1786</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
         <v>-0.5893</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>F. GARRIDO TEBAN</t>
+          <t>J. TOMAIC TOMAIC</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.3302</v>
+        <v>-2.491</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.37</v>
+        <v>-1.9497</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.9603</v>
+        <v>-0.5414</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.1183</v>
+        <v>-2.1166</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.8501</v>
+        <v>-4.2136</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.2682</v>
+        <v>2.097</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.5795</v>
+        <v>-0.4045</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.6584</v>
+        <v>-2.8249</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0789</v>
+        <v>2.4204</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.5387999999999999</v>
+        <v>-1.7121</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.1917</v>
+        <v>-1.3887</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.3472</v>
+        <v>-0.3234</v>
       </c>
       <c r="P18" t="n">
-        <v>0.2053</v>
+        <v>-0.8214</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-2.0534</v>
       </c>
       <c r="R18" t="n">
-        <v>0.2053</v>
+        <v>1.2321</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.828</v>
+        <v>-0.1424</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.7905</v>
+        <v>-0.6704</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0375</v>
+        <v>0.528</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.5893</v>
+        <v>0.5893</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.1786</v>
       </c>
       <c r="X18" t="n">
         <v>-0.5893</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>G. MARTINEZ RIVERA</t>
+          <t>E. COLL COMABELLA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.8575</v>
+        <v>-3.0019</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.4419</v>
+        <v>-0.8437</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5843</v>
+        <v>-2.1581</v>
       </c>
       <c r="G19" t="n">
-        <v>-6.0051</v>
+        <v>-1.9026</v>
       </c>
       <c r="H19" t="n">
-        <v>-4.7001</v>
+        <v>-1.8264</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.3051</v>
+        <v>-0.07630000000000001</v>
       </c>
       <c r="J19" t="n">
-        <v>-4.8954</v>
+        <v>-0.619</v>
       </c>
       <c r="K19" t="n">
-        <v>-4.8425</v>
+        <v>-0.6584</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.0529</v>
+        <v>0.0395</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.1097</v>
+        <v>-1.2837</v>
       </c>
       <c r="N19" t="n">
-        <v>0.1425</v>
+        <v>-1.1679</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.2522</v>
+        <v>-0.1157</v>
       </c>
       <c r="P19" t="n">
-        <v>1.4374</v>
+        <v>0.2053</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.4374</v>
+        <v>0.2053</v>
       </c>
       <c r="S19" t="n">
-        <v>0.5315</v>
+        <v>-0.1259</v>
       </c>
       <c r="T19" t="n">
-        <v>0.2749</v>
+        <v>-0.2248</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2567</v>
+        <v>0.0988</v>
       </c>
       <c r="V19" t="n">
-        <v>1.1786</v>
+        <v>-1.1786</v>
       </c>
       <c r="W19" t="n">
-        <v>1.1786</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>E. COLL COMABELLA</t>
+          <t>N. FERRER IGLESIA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,58 +1969,58 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.1657</v>
+        <v>-3.5681</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.9483</v>
+        <v>-2.7779</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.2174</v>
+        <v>-0.7902</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.9026</v>
+        <v>-0.4736</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.8264</v>
+        <v>0.0843</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.07630000000000001</v>
+        <v>-0.5579</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.619</v>
+        <v>-0.6974</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.6584</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0395</v>
+        <v>-0.6974</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.2837</v>
+        <v>0.2238</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.1679</v>
+        <v>0.0843</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.1157</v>
+        <v>0.1395</v>
       </c>
       <c r="P20" t="n">
-        <v>0.2053</v>
+        <v>-1.8481</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-2.0534</v>
       </c>
       <c r="R20" t="n">
         <v>0.2053</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2898</v>
+        <v>-0.0678</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3294</v>
+        <v>-0.0271</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0395</v>
+        <v>-0.0407</v>
       </c>
       <c r="V20" t="n">
         <v>-1.1786</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>N. FERRER IGLESIA</t>
+          <t>G. MARTINEZ RIVERA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.732</v>
+        <v>-3.8269</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.8825</v>
+        <v>-4.1741</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.8495</v>
+        <v>0.3472</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.4736</v>
+        <v>-6.0051</v>
       </c>
       <c r="H21" t="n">
-        <v>0.0843</v>
+        <v>-4.7001</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.5579</v>
+        <v>-1.3051</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.6974</v>
+        <v>-4.8954</v>
       </c>
       <c r="K21" t="n">
+        <v>-4.8425</v>
+      </c>
+      <c r="L21" t="n">
+        <v>-0.0529</v>
+      </c>
+      <c r="M21" t="n">
+        <v>-1.1097</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0.1425</v>
+      </c>
+      <c r="O21" t="n">
+        <v>-1.2522</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1.4374</v>
+      </c>
+      <c r="Q21" t="n">
         <v>0</v>
       </c>
-      <c r="L21" t="n">
-        <v>-0.6974</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0.2238</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0.0843</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0.1395</v>
-      </c>
-      <c r="P21" t="n">
-        <v>-1.8481</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>-2.0534</v>
-      </c>
       <c r="R21" t="n">
-        <v>0.2053</v>
+        <v>1.4374</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2317</v>
+        <v>-0.4378</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1317</v>
+        <v>-0.4573</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0999</v>
+        <v>0.0195</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.1786</v>
+        <v>1.1786</v>
       </c>
       <c r="W21" t="n">
+        <v>1.1786</v>
+      </c>
+      <c r="X21" t="n">
         <v>0</v>
-      </c>
-      <c r="X21" t="n">
-        <v>-1.1786</v>
       </c>
     </row>
     <row r="22">
@@ -2125,19 +2125,19 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.851599999999999</v>
+        <v>-4.456999999999999</v>
       </c>
       <c r="E22" t="n">
         <v>-4.0716</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.7803</v>
+        <v>-0.3855999999999997</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.3529999999999991</v>
+        <v>-0.3529999999999989</v>
       </c>
       <c r="H22" t="n">
-        <v>-9.181000000000001</v>
+        <v>-9.180999999999999</v>
       </c>
       <c r="I22" t="n">
         <v>8.827999999999999</v>
@@ -2170,19 +2170,19 @@
         <v>15.4005</v>
       </c>
       <c r="S22" t="n">
-        <v>-6.1989</v>
+        <v>-4.804200000000001</v>
       </c>
       <c r="T22" t="n">
-        <v>-5.2901</v>
+        <v>-5.29</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.9087000000000001</v>
+        <v>0.4858</v>
       </c>
       <c r="V22" t="n">
         <v>-0.3264999999999998</v>
       </c>
       <c r="W22" t="n">
-        <v>7.7061</v>
+        <v>7.706100000000001</v>
       </c>
       <c r="X22" t="n">
         <v>-8.0327</v>
